--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_ui/lang_ui__ui__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_ui/lang_ui__ui__part_0001.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
     </row>
